--- a/results/Int All Data -0.9/Linea_fi_explain.xlsx
+++ b/results/Int All Data -0.9/Linea_fi_explain.xlsx
@@ -1685,7 +1685,7 @@
         <v>0.0003111239570784041</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001548644845314605</v>
+        <v>0.001554539333967714</v>
       </c>
       <c r="F3" t="n">
         <v>-3.47783015178249e-05</v>
@@ -1694,13 +1694,13 @@
         <v>0.01127210660661828</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01447921302311928</v>
+        <v>0.01448510751177239</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007023574578582744</v>
+        <v>0.00700883835694997</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0006157562439649244</v>
+        <v>-0.0006187034882914787</v>
       </c>
       <c r="K3" t="n">
         <v>0.00140144670154023</v>
@@ -1712,7 +1712,7 @@
         <v>-0.0002084423910310107</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001363789168146063</v>
+        <v>0.001366736412472619</v>
       </c>
       <c r="O3" t="n">
         <v>-0.0008654051542286723</v>
@@ -1724,7 +1724,7 @@
         <v>0.04098214699356687</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003224048855641944</v>
+        <v>0.003229943344295054</v>
       </c>
       <c r="S3" t="n">
         <v>0.01205981640642361</v>
@@ -1736,7 +1736,7 @@
         <v>0.001484483590132357</v>
       </c>
       <c r="V3" t="n">
-        <v>0.006988207646664087</v>
+        <v>0.00700883835694997</v>
       </c>
       <c r="W3" t="n">
         <v>0.006029395629926111</v>
@@ -1751,7 +1751,7 @@
         <v>-0.0004590036113626027</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.0007498830220903096</v>
+        <v>-0.0007380940447840922</v>
       </c>
       <c r="AB3" t="n">
         <v>1.06564579958301e-05</v>
@@ -1760,13 +1760,13 @@
         <v>0.003480428441418658</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.003093766718137368</v>
+        <v>-0.003102601485694695</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.006516165635862441</v>
+        <v>0.006519112880188996</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.001276463032336752</v>
+        <v>-0.001285304765316415</v>
       </c>
       <c r="AG3" t="n">
         <v>0.0004834180049254667</v>
@@ -1778,10 +1778,10 @@
         <v>-0.0009707728312393939</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.0199246406624372</v>
+        <v>0.01992758790676375</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.02562633261796214</v>
+        <v>0.0256292798622887</v>
       </c>
       <c r="AL3" t="n">
         <v>0.01465608839470417</v>
@@ -1790,7 +1790,7 @@
         <v>0.1360234908702216</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.0004691065779511006</v>
+        <v>-0.0004425813790121092</v>
       </c>
       <c r="AO3" t="n">
         <v>0.00437791919388385</v>
@@ -1802,7 +1802,7 @@
         <v>0.002405816609725255</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.006525007368842104</v>
+        <v>0.006519112880188996</v>
       </c>
       <c r="AS3" t="n">
         <v>0.006791764257994544</v>
@@ -1817,7 +1817,7 @@
         <v>-0.0002520164973282034</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.002140367523386344</v>
+        <v>-0.002137420279059793</v>
       </c>
       <c r="AX3" t="n">
         <v>0.0006587064567587931</v>
@@ -1826,10 +1826,10 @@
         <v>0.06420866926988018</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.0006995809586042279</v>
+        <v>-0.0006934999004262144</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.006416567047185413</v>
+        <v>0.00641361980285886</v>
       </c>
       <c r="BB3" t="n">
         <v>0.01597661677563035</v>
@@ -1856,7 +1856,7 @@
         <v>0.06504424860428615</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.01073365544091409</v>
+        <v>0.01071302473062821</v>
       </c>
       <c r="BK3" t="n">
         <v>0.1113877929429124</v>
@@ -1868,7 +1868,7 @@
         <v>0.003689952115753654</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.006416567047185415</v>
+        <v>0.00641361980285886</v>
       </c>
       <c r="BO3" t="n">
         <v>0.01171568289048632</v>
@@ -1883,7 +1883,7 @@
         <v>0.00696697792528019</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.003476475927653614</v>
+        <v>0.003494182077605777</v>
       </c>
       <c r="BT3" t="n">
         <v>-0.00123911482743192</v>
@@ -1892,28 +1892,28 @@
         <v>0.001855847269032266</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.0008544629452927402</v>
+        <v>0.0007511228243384239</v>
       </c>
       <c r="BW3" t="n">
         <v>0.0001837026616162607</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.007716866893626997</v>
+        <v>0.007752233825545652</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.0002414416486139337</v>
+        <v>0.000259125114573262</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.0003003743240113866</v>
+        <v>0.0002561656591130668</v>
       </c>
       <c r="CA3" t="n">
         <v>0.009726126393306616</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0.0001982242022447943</v>
+        <v>-0.000195276957918241</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.0195018116007503</v>
+        <v>0.01949886435642375</v>
       </c>
       <c r="CD3" t="n">
         <v>-0.002040150128847263</v>
@@ -1922,7 +1922,7 @@
         <v>0.001127930687359982</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.00104589604640861</v>
+        <v>0.001122522660624583</v>
       </c>
       <c r="CG3" t="n">
         <v>0.4057770904990224</v>
@@ -1949,7 +1949,7 @@
         <v>0.002952588659473627</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.0460528723137299</v>
+        <v>0.04604992506940334</v>
       </c>
       <c r="CP3" t="n">
         <v>-0.0003613867691417594</v>
@@ -1958,13 +1958,13 @@
         <v>0.08230632754221129</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.09317618716625448</v>
+        <v>0.09316734543327482</v>
       </c>
       <c r="CS3" t="n">
         <v>0.3294268870620005</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.1063515886921348</v>
+        <v>0.1063574831807879</v>
       </c>
       <c r="CU3" t="n">
         <v>0.04575040077619338</v>
@@ -1976,10 +1976,10 @@
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.06666527304412642</v>
+        <v>0.06669474548739199</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.09042076618108963</v>
+        <v>0.09038834649349752</v>
       </c>
       <c r="CZ3" t="n">
         <v>-0.0006744709036788154</v>
@@ -2024,19 +2024,19 @@
         <v>-0.001060154034387272</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.00517519666213082</v>
+        <v>0.005198774616743259</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.005921242074139724</v>
+        <v>0.005947767273078714</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0.0001939955206315913</v>
+        <v>-0.0002057844979378098</v>
       </c>
       <c r="DQ3" t="n">
         <v>-0.0001469314931544696</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0.0001528259818075794</v>
+        <v>-0.0001469314931544696</v>
       </c>
       <c r="DS3" t="n">
         <v>-0.0002456811450123153</v>
@@ -2054,7 +2054,7 @@
         <v>0.0008726076908069204</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.006731550978849662</v>
+        <v>0.006731484748640078</v>
       </c>
       <c r="DY3" t="n">
         <v>0.009739229838522264</v>
@@ -2066,7 +2066,7 @@
         <v>0.03631976284324757</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.005962503494711486</v>
+        <v>0.005947767273078714</v>
       </c>
       <c r="EC3" t="n">
         <v>0.002181231210617141</v>
@@ -2090,7 +2090,7 @@
         <v>0.01955257593836337</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.0003225248286028506</v>
+        <v>-0.0003048413626435223</v>
       </c>
       <c r="EK3" t="n">
         <v>0.00953089669062215</v>
@@ -2102,7 +2102,7 @@
         <v>-0.0001731576641312882</v>
       </c>
       <c r="EN3" t="n">
-        <v>-0.0001761049084578425</v>
+        <v>-0.0001731576641312882</v>
       </c>
       <c r="EO3" t="n">
         <v>0.0002752157166084013</v>
@@ -2111,7 +2111,7 @@
         <v>0.001505098125144025</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.01112001920696624</v>
+        <v>0.01111707196263969</v>
       </c>
       <c r="ER3" t="n">
         <v>-0.0004818681663945267</v>
@@ -2154,7 +2154,7 @@
         <v>0.001873841071102611</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003502941354599567</v>
+        <v>0.003502299575518863</v>
       </c>
       <c r="F4" t="n">
         <v>0.001022081441935697</v>
@@ -2163,13 +2163,13 @@
         <v>0.01603416688699064</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01723512794061936</v>
+        <v>0.01723103532239286</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01607798954809718</v>
+        <v>0.01607230263234145</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003487092313043495</v>
+        <v>0.003482094537388855</v>
       </c>
       <c r="K4" t="n">
         <v>0.008338971659295953</v>
@@ -2181,7 +2181,7 @@
         <v>0.003367171773006526</v>
       </c>
       <c r="N4" t="n">
-        <v>0.008525233252172656</v>
+        <v>0.008525042793278738</v>
       </c>
       <c r="O4" t="n">
         <v>0.01343414537647754</v>
@@ -2193,7 +2193,7 @@
         <v>0.03681214709606026</v>
       </c>
       <c r="R4" t="n">
-        <v>0.005791522572604454</v>
+        <v>0.005780797519158423</v>
       </c>
       <c r="S4" t="n">
         <v>0.0184725199343545</v>
@@ -2205,7 +2205,7 @@
         <v>0.01184912761855595</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01606456466731726</v>
+        <v>0.01607230263234145</v>
       </c>
       <c r="W4" t="n">
         <v>0.01540449443855922</v>
@@ -2220,7 +2220,7 @@
         <v>0.00315275344357137</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.004011067413148333</v>
+        <v>0.004022335990018482</v>
       </c>
       <c r="AB4" t="n">
         <v>0.0008690575469803593</v>
@@ -2229,13 +2229,13 @@
         <v>0.007954411899760636</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.004569745134035345</v>
+        <v>0.004546845578882306</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.004270871460338927</v>
+        <v>0.004273274246699023</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.003378034803191355</v>
+        <v>0.003375637382328144</v>
       </c>
       <c r="AG4" t="n">
         <v>0.001308502594776098</v>
@@ -2247,10 +2247,10 @@
         <v>0.001696544224376826</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.01647622284706676</v>
+        <v>0.01647602020773921</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.01376267497381192</v>
+        <v>0.01375895736560777</v>
       </c>
       <c r="AL4" t="n">
         <v>0.01652556858171203</v>
@@ -2259,7 +2259,7 @@
         <v>0.03297911104544203</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.001292808880789391</v>
+        <v>0.001301491970499701</v>
       </c>
       <c r="AO4" t="n">
         <v>0.01046850000292252</v>
@@ -2271,7 +2271,7 @@
         <v>0.004861682878068957</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.004278136682713094</v>
+        <v>0.004273274246699023</v>
       </c>
       <c r="AS4" t="n">
         <v>0.01668023848324465</v>
@@ -2286,7 +2286,7 @@
         <v>0.004073346959111102</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.006501201058167951</v>
+        <v>0.006502612310686872</v>
       </c>
       <c r="AX4" t="n">
         <v>0.004906892166838463</v>
@@ -2295,10 +2295,10 @@
         <v>0.04259933152648635</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.002092859452126968</v>
+        <v>0.00209168382731354</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.006810540016798388</v>
+        <v>0.006811463411367319</v>
       </c>
       <c r="BB4" t="n">
         <v>0.01370447239656706</v>
@@ -2325,7 +2325,7 @@
         <v>0.03948419690786498</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.01206967436179424</v>
+        <v>0.01210445973279906</v>
       </c>
       <c r="BK4" t="n">
         <v>0.08070830461581534</v>
@@ -2337,7 +2337,7 @@
         <v>0.004635619349422691</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.006810540016798388</v>
+        <v>0.006811463411367319</v>
       </c>
       <c r="BO4" t="n">
         <v>0.01623661388386808</v>
@@ -2352,7 +2352,7 @@
         <v>0.01619114430883199</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.01001816213020051</v>
+        <v>0.01001370161456216</v>
       </c>
       <c r="BT4" t="n">
         <v>0.001271287896368118</v>
@@ -2361,28 +2361,28 @@
         <v>0.01180571118940769</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.008590347121726193</v>
+        <v>0.008356134453116641</v>
       </c>
       <c r="BW4" t="n">
         <v>0.0003542852219701615</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.01528744302677161</v>
+        <v>0.0152469769168383</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.002189048363061136</v>
+        <v>0.002158280248566059</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.002086577083545701</v>
+        <v>0.002158830530807663</v>
       </c>
       <c r="CA4" t="n">
         <v>0.01645424058585193</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.008138187144317044</v>
+        <v>0.008139825658492182</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.02985637462448342</v>
+        <v>0.02985861520945449</v>
       </c>
       <c r="CD4" t="n">
         <v>0.01022698791496456</v>
@@ -2391,7 +2391,7 @@
         <v>0.004344552135893899</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.002307267026251338</v>
+        <v>0.002279176771701213</v>
       </c>
       <c r="CG4" t="n">
         <v>0.08246576340760917</v>
@@ -2418,7 +2418,7 @@
         <v>0.005745658107105863</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.03242837417787329</v>
+        <v>0.03242810936478042</v>
       </c>
       <c r="CP4" t="n">
         <v>0.0005891204806278798</v>
@@ -2427,13 +2427,13 @@
         <v>0.04353134957740604</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.05581196095015471</v>
+        <v>0.05582671217758896</v>
       </c>
       <c r="CS4" t="n">
         <v>0.1109533451405883</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.06774941679632834</v>
+        <v>0.06773897784600764</v>
       </c>
       <c r="CU4" t="n">
         <v>0.05223812966316584</v>
@@ -2445,10 +2445,10 @@
         <v>0</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.06746615129677365</v>
+        <v>0.06746049390042817</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.07390003070840563</v>
+        <v>0.07387277220068496</v>
       </c>
       <c r="CZ4" t="n">
         <v>0.002307109967971574</v>
@@ -2493,19 +2493,19 @@
         <v>0.002940974795580604</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.01035079742802151</v>
+        <v>0.01038929154545679</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.01676833423295909</v>
+        <v>0.01685071085452368</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.006728010981314316</v>
+        <v>0.006721995850898504</v>
       </c>
       <c r="DQ4" t="n">
         <v>0.00158589829706631</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.001582842082192263</v>
+        <v>0.00158589829706631</v>
       </c>
       <c r="DS4" t="n">
         <v>0.00299067242506133</v>
@@ -2523,7 +2523,7 @@
         <v>0.003501163665459609</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.01073409135830551</v>
+        <v>0.0107384842289019</v>
       </c>
       <c r="DY4" t="n">
         <v>0.02848587163961338</v>
@@ -2535,7 +2535,7 @@
         <v>0.01564317148988357</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.01689648203643123</v>
+        <v>0.01685071085452368</v>
       </c>
       <c r="EC4" t="n">
         <v>0.009632862137900643</v>
@@ -2559,7 +2559,7 @@
         <v>0.02235341551258474</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.01044185230154529</v>
+        <v>0.01045690621708905</v>
       </c>
       <c r="EK4" t="n">
         <v>0.02141566376520908</v>
@@ -2571,7 +2571,7 @@
         <v>0.001248981185179625</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.001247556579177334</v>
+        <v>0.001248981185179625</v>
       </c>
       <c r="EO4" t="n">
         <v>0.0005307650271478676</v>
@@ -2580,7 +2580,7 @@
         <v>0.005589075391569021</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.0126912506740341</v>
+        <v>0.01269522545551774</v>
       </c>
       <c r="ER4" t="n">
         <v>0.007657736360274402</v>
@@ -2662,7 +2662,7 @@
         <v>-0.0001222493887530707</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.00627763041556142</v>
+        <v>-0.006218685529030321</v>
       </c>
       <c r="S5" t="n">
         <v>-0.02064287820701854</v>
@@ -2719,7 +2719,7 @@
         <v>-0.002279455298993449</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.009991158267020361</v>
+        <v>0.01002063071028592</v>
       </c>
       <c r="AL5" t="n">
         <v>-0.01010920436817474</v>
@@ -2770,7 +2770,7 @@
         <v>-0.003601267646211481</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.004391394046566443</v>
+        <v>-0.004391394046566433</v>
       </c>
       <c r="BC5" t="n">
         <v>-0.00166092134127237</v>
@@ -2794,7 +2794,7 @@
         <v>0.004128575641403754</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.007515473032714393</v>
+        <v>-0.007721780135573231</v>
       </c>
       <c r="BK5" t="n">
         <v>-0.009680207433016442</v>
@@ -2836,13 +2836,13 @@
         <v>-0.0004321521175453813</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.008163866784556406</v>
+        <v>-0.007810197465369861</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.003241968759210112</v>
+        <v>-0.003065134099616828</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.002623047450633631</v>
+        <v>-0.003065134099616828</v>
       </c>
       <c r="CA5" t="n">
         <v>-0.01915874387784502</v>
@@ -2896,13 +2896,13 @@
         <v>0.01299734748010614</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.009401709401709424</v>
+        <v>0.009313292071912782</v>
       </c>
       <c r="CS5" t="n">
         <v>0.1066607721780136</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0.001650456822870583</v>
+        <v>-0.001591511936339496</v>
       </c>
       <c r="CU5" t="n">
         <v>-0.008210890233362144</v>
@@ -2992,7 +2992,7 @@
         <v>-0.006984314886060938</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.01013852048334804</v>
+        <v>-0.01016799292661359</v>
       </c>
       <c r="DY5" t="n">
         <v>-0.02606900619286341</v>
@@ -3049,7 +3049,7 @@
         <v>-0.001974653698791606</v>
       </c>
       <c r="EQ5" t="n">
-        <v>-0.004273504273504258</v>
+        <v>-0.004302976716769802</v>
       </c>
       <c r="ER5" t="n">
         <v>-0.01863757003833674</v>
@@ -3101,7 +3101,7 @@
         <v>0.001669406142444976</v>
       </c>
       <c r="H6" t="n">
-        <v>0.006179578217611492</v>
+        <v>0.006223786882509816</v>
       </c>
       <c r="I6" t="n">
         <v>0.005652106801577519</v>
@@ -3233,7 +3233,7 @@
         <v>0.03214119088383055</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.001001053835256843</v>
+        <v>-0.0009940215306155798</v>
       </c>
       <c r="BA6" t="n">
         <v>0.003055431444535334</v>
@@ -3320,7 +3320,7 @@
         <v>-0.004023455227322691</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.0001197878506491808</v>
+        <v>9.768351820002292e-05</v>
       </c>
       <c r="CD6" t="n">
         <v>-0.001363266076555494</v>
@@ -3329,7 +3329,7 @@
         <v>-0.0002907301939516632</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.0001411491947258425</v>
+        <v>-0.0001632665642333581</v>
       </c>
       <c r="CG6" t="n">
         <v>0.3371997267952399</v>
@@ -3561,7 +3561,7 @@
         <v>-0.0001464302290533959</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001353879442534039</v>
+        <v>0.001383351885799583</v>
       </c>
       <c r="F7" t="n">
         <v>-0.0001772413620645952</v>
@@ -3588,7 +3588,7 @@
         <v>0.0006063591398675627</v>
       </c>
       <c r="N7" t="n">
-        <v>0.002994587591164621</v>
+        <v>0.003009323812797399</v>
       </c>
       <c r="O7" t="n">
         <v>0.00104793901977821</v>
@@ -3654,7 +3654,7 @@
         <v>-0.0004536088625218759</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.01895847345804055</v>
+        <v>0.01897320967967332</v>
       </c>
       <c r="AK7" t="n">
         <v>0.0225384727964208</v>
@@ -3666,7 +3666,7 @@
         <v>0.1322237324886312</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.000592925951314166</v>
+        <v>-0.0004897723998847692</v>
       </c>
       <c r="AO7" t="n">
         <v>0.0003104675050046135</v>
@@ -3702,10 +3702,10 @@
         <v>0.06009823510703161</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-0.0002366252940330438</v>
+        <v>-0.0002359536816827934</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.005791191184747774</v>
+        <v>0.005776454963115002</v>
       </c>
       <c r="BB7" t="n">
         <v>0.01419884524041629</v>
@@ -3744,7 +3744,7 @@
         <v>0.001923838054328747</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.005791191184747779</v>
+        <v>0.005776454963115002</v>
       </c>
       <c r="BO7" t="n">
         <v>0.01419215714515754</v>
@@ -3759,7 +3759,7 @@
         <v>0.0006122693076588081</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.0001305501019760679</v>
+        <v>0.0002338257647418907</v>
       </c>
       <c r="BT7" t="n">
         <v>-0.001133906772839444</v>
@@ -3798,7 +3798,7 @@
         <v>0.001017809278900334</v>
       </c>
       <c r="CF7" t="n">
-        <v>-7.381198046962356e-05</v>
+        <v>8.856507438436689e-05</v>
       </c>
       <c r="CG7" t="n">
         <v>0.41965042453222</v>
@@ -3825,7 +3825,7 @@
         <v>0.00245329716653806</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.04918141990169922</v>
+        <v>0.04916668368006645</v>
       </c>
       <c r="CP7" t="n">
         <v>-0.000221749385414155</v>
@@ -3852,7 +3852,7 @@
         <v>0</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.06110265053994582</v>
+        <v>0.06125001275627354</v>
       </c>
       <c r="CY7" t="n">
         <v>0.1081700956995709</v>
@@ -3930,7 +3930,7 @@
         <v>0.00108653723588712</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.004525958277638731</v>
+        <v>0.004540363348223581</v>
       </c>
       <c r="DY7" t="n">
         <v>0.00444465012355223</v>
@@ -3978,7 +3978,7 @@
         <v>-2.2365549091774e-05</v>
       </c>
       <c r="EN7" t="n">
-        <v>-3.710177072454581e-05</v>
+        <v>-2.2365549091774e-05</v>
       </c>
       <c r="EO7" t="n">
         <v>0.0002367914806931992</v>
@@ -4042,7 +4042,7 @@
         <v>0.01946744655085089</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01416062029628371</v>
+        <v>0.01412377974220178</v>
       </c>
       <c r="J8" t="n">
         <v>0.0002959543069889243</v>
@@ -4081,7 +4081,7 @@
         <v>0.007013728243133558</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01407220296648707</v>
+        <v>0.01412377974220178</v>
       </c>
       <c r="W8" t="n">
         <v>0.01626002336781662</v>
@@ -4096,7 +4096,7 @@
         <v>0.0006099606343878128</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.002218747718589581</v>
+        <v>0.002307165048386212</v>
       </c>
       <c r="AB8" t="n">
         <v>0.0002956402676785208</v>
@@ -4108,10 +4108,10 @@
         <v>-0.0007611504803489155</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.009084901417863767</v>
+        <v>0.009107005750312924</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0006295285089613827</v>
+        <v>0.000607424176512225</v>
       </c>
       <c r="AG8" t="n">
         <v>0.001319804905693864</v>
@@ -4135,7 +4135,7 @@
         <v>0.163439411463629</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.0002663509914175744</v>
+        <v>0.0002810872130503544</v>
       </c>
       <c r="AO8" t="n">
         <v>0.01044521608497965</v>
@@ -4147,7 +4147,7 @@
         <v>0.006758260378834949</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.00915121441521124</v>
+        <v>0.009107005750312924</v>
       </c>
       <c r="AS8" t="n">
         <v>0.01536558986122527</v>
@@ -4162,7 +4162,7 @@
         <v>0.001821554876728021</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.001201614804813966</v>
+        <v>0.001208982915630347</v>
       </c>
       <c r="AX8" t="n">
         <v>0.003351157425238124</v>
@@ -4255,7 +4255,7 @@
         <v>0.0206098212919942</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.00287347163488853</v>
+        <v>0.00289557596733768</v>
       </c>
       <c r="CC8" t="n">
         <v>0.02479492228691446</v>
@@ -4267,7 +4267,7 @@
         <v>0.001829184667379938</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.0007915494213761754</v>
+        <v>0.0009092998859916185</v>
       </c>
       <c r="CG8" t="n">
         <v>0.4504776755901497</v>
@@ -4324,7 +4324,7 @@
         <v>0.1128391407384429</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.1449840861866533</v>
+        <v>0.1447409385297126</v>
       </c>
       <c r="CZ8" t="n">
         <v>0.0009613345792178568</v>
@@ -4375,13 +4375,13 @@
         <v>0.004225055932331972</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.003134178678003419</v>
+        <v>0.003104706234737872</v>
       </c>
       <c r="DQ8" t="n">
         <v>0.0004953922294823054</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0004511835645839819</v>
+        <v>0.0004953922294823054</v>
       </c>
       <c r="DS8" t="n">
         <v>0.0005334093180069666</v>
@@ -4574,7 +4574,7 @@
         <v>0.02485114384205573</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.005835543766578277</v>
+        <v>0.005717653993516081</v>
       </c>
       <c r="AE9" t="n">
         <v>0.01419656786271451</v>
@@ -4706,7 +4706,7 @@
         <v>0.02270782396088021</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.01889183613321547</v>
+        <v>0.01788977306218687</v>
       </c>
       <c r="BW9" t="n">
         <v>0.0006864274570983042</v>
@@ -4841,7 +4841,7 @@
         <v>0.0280190362879239</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.05278514588859421</v>
+        <v>0.05305039787798412</v>
       </c>
       <c r="DP9" t="n">
         <v>0.00553242117787035</v>
@@ -4880,7 +4880,7 @@
         <v>0.05691032849955611</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.05319776009431184</v>
+        <v>0.05305039787798412</v>
       </c>
       <c r="EC9" t="n">
         <v>0.02114812611540752</v>
